--- a/model_maker_web_v2/results/Huawei/Huawei_stage2.xlsx
+++ b/model_maker_web_v2/results/Huawei/Huawei_stage2.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SUN2000MC</t>
+          <t>Huawei</t>
         </is>
       </c>
     </row>
@@ -24322,7 +24322,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SUN2000MC</t>
+          <t>Huawei</t>
         </is>
       </c>
     </row>
